--- a/outputs/development-prep-20261026/架构配置.xlsx
+++ b/outputs/development-prep-20261026/架构配置.xlsx
@@ -2866,6 +2866,54 @@
         <x:v>pending</x:v>
       </x:c>
     </x:row>
+    <x:row r="43" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A43" s="18">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B43" s="16" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">candidate</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C43" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">本任务rule16技术候选；docs/职业宠物生命周期与召唤实施边界.md</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D43" s="17" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">包括同owner全部World的活动宠、尸体及待新生reservation；满额只拒新生不拒死亡，不丢弃未过期原尸体。101仅180s/1800ms典型源路径估计，不证明通用上界或整机容量。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E43" s="16" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">retained_pet_body_capacity_per_owner</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F43" s="19">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="G43" s="16" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">身体/owner</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H43" s="16" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">同owner全部保留World的宠物身体与新生预留</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I43" s="16" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">adapt</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J43" s="16" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">pending</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="A4:A1003">
     <x:cfRule type="expression" dxfId="11" priority="1">
